--- a/results/supplementary_bio_results.xlsx
+++ b/results/supplementary_bio_results.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="455">
   <si>
     <t>software</t>
   </si>
@@ -5434,20 +5434,31 @@
     return str(nonlog_val)</t>
   </si>
   <si>
-    <t>assert covertLogFoldToNonLog("-1") == -2.0
-assert covertLogFoldToNonLog("0") == 1.0
-assert covertLogFoldToNonLog("1") == 2.0
-assert covertLogFoldToNonLog("2") == 4.0
-assert covertLogFoldToNonLog("-0.5") == -1.414213562373095
-assert covertLogFoldToNonLog("3.5") == 11.313708498984761</t>
-  </si>
-  <si>
-    <t>covertLogFoldToNonLog("-1") == -0.5
-covertLogFoldToNonLog("0") == 1.0
-covertLogFoldToNonLog("1") == 2.0
-covertLogFoldToNonLog("2") == 4.0
-covertLogFoldToNonLog("-0.5") == -0.7071067811865476
-covertLogFoldToNonLog("3.5") == 11.313708498984761</t>
+    <t>def covertLogFoldToNonLogFloat(log_val):
+    try:
+        if float(log_val) &lt; 0:
+            nonlog_val = (-1 * math.pow(2, (float(log_val))))
+        else:
+            nonlog_val = (math.pow(2, float(log_val)))
+    except Exception:
+        nonlog_val = log_val
+    return str(nonlog_val)</t>
+  </si>
+  <si>
+    <t>assert covertLogFoldToNonLogFloat("-1") == '-0.5'
+assert covertLogFoldToNonLogFloat("0") == '1.0'
+assert covertLogFoldToNonLogFloat("1") == '2.0'
+assert covertLogFoldToNonLogFloat("2") == '4.0'
+assert covertLogFoldToNonLogFloat("abc") == 'abc'
+assert covertLogFoldToNonLogFloat("-abc") == '-abc'
+assert covertLogFoldToNonLogFloat("-0.5") == '-0.7071067811865476'
+assert covertLogFoldToNonLogFloat("3.5") == '11.313708498984761'
+assert covertLogFoldToNonLogFloat("-3.5") == '-0.08838834764831845'</t>
+  </si>
+  <si>
+    <t>covertLogFoldToNonLogFloat("-1") == '-2.0'
+covertLogFoldToNonLogFloat("-0.5") == '-1.414213562373095'
+covertLogFoldToNonLogFloat("-3.5") == '-11.31370849898476'</t>
   </si>
   <si>
     <t>def predictIDSource(id,system_codes):
@@ -6894,7 +6905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
@@ -6934,7 +6945,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="409.5" spans="1:8">
+    <row r="2" ht="409.5" hidden="1" spans="1:8">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -6960,7 +6971,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="297" spans="1:8">
+    <row r="3" ht="297" hidden="1" spans="1:8">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -6986,7 +6997,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="409.5" spans="1:8">
+    <row r="4" ht="409.5" hidden="1" spans="1:8">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -7012,7 +7023,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="409.5" spans="1:8">
+    <row r="5" ht="409.5" hidden="1" spans="1:8">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -7038,7 +7049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" ht="243" spans="1:8">
+    <row r="6" ht="243" hidden="1" spans="1:8">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -7061,7 +7072,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" ht="121.5" spans="1:8">
+    <row r="7" ht="121.5" hidden="1" spans="1:8">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -7084,7 +7095,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" ht="270" spans="1:8">
+    <row r="8" ht="270" hidden="1" spans="1:8">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -7107,7 +7118,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" ht="409.5" spans="1:8">
+    <row r="9" ht="409.5" hidden="1" spans="1:8">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -7133,7 +7144,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" ht="175.5" spans="1:8">
+    <row r="10" ht="175.5" hidden="1" spans="1:8">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -7156,7 +7167,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" ht="256.5" spans="1:8">
+    <row r="11" ht="256.5" hidden="1" spans="1:8">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -7182,7 +7193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" ht="256.5" spans="1:8">
+    <row r="12" ht="256.5" hidden="1" spans="1:8">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -7208,7 +7219,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" ht="216" spans="1:8">
+    <row r="13" ht="216" hidden="1" spans="1:8">
       <c r="A13" t="s">
         <v>70</v>
       </c>
@@ -7234,7 +7245,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" ht="162" spans="1:8">
+    <row r="14" ht="162" hidden="1" spans="1:8">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -7260,7 +7271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" ht="216" spans="1:8">
+    <row r="15" ht="216" hidden="1" spans="1:8">
       <c r="A15" t="s">
         <v>70</v>
       </c>
@@ -7286,7 +7297,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" ht="297" spans="1:8">
+    <row r="16" ht="297" hidden="1" spans="1:8">
       <c r="A16" t="s">
         <v>70</v>
       </c>
@@ -7312,7 +7323,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" ht="409.5" spans="1:8">
+    <row r="17" ht="409.5" hidden="1" spans="1:8">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -7338,7 +7349,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" ht="189" spans="1:8">
+    <row r="18" ht="189" hidden="1" spans="1:8">
       <c r="A18" t="s">
         <v>70</v>
       </c>
@@ -7364,7 +7375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="189" spans="1:8">
+    <row r="19" ht="189" hidden="1" spans="1:8">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -7390,7 +7401,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" ht="148.5" spans="1:8">
+    <row r="20" ht="148.5" hidden="1" spans="1:8">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -7413,7 +7424,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" ht="310.5" spans="1:8">
+    <row r="21" ht="310.5" hidden="1" spans="1:8">
       <c r="A21" t="s">
         <v>70</v>
       </c>
@@ -7439,7 +7450,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" ht="337.5" spans="1:8">
+    <row r="22" ht="337.5" hidden="1" spans="1:8">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -7462,7 +7473,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" ht="409.5" spans="1:8">
+    <row r="23" ht="409.5" hidden="1" spans="1:8">
       <c r="A23" t="s">
         <v>70</v>
       </c>
@@ -7488,7 +7499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" ht="364.5" spans="1:8">
+    <row r="24" ht="364.5" hidden="1" spans="1:8">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -7511,7 +7522,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" ht="162" spans="1:8">
+    <row r="25" ht="162" hidden="1" spans="1:8">
       <c r="A25" t="s">
         <v>70</v>
       </c>
@@ -7537,7 +7548,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" ht="364.5" spans="1:8">
+    <row r="26" ht="364.5" hidden="1" spans="1:8">
       <c r="A26" t="s">
         <v>70</v>
       </c>
@@ -7560,7 +7571,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" ht="108" spans="1:8">
+    <row r="27" ht="108" hidden="1" spans="1:8">
       <c r="A27" t="s">
         <v>70</v>
       </c>
@@ -7583,7 +7594,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" ht="108" spans="1:8">
+    <row r="28" ht="108" hidden="1" spans="1:8">
       <c r="A28" t="s">
         <v>70</v>
       </c>
@@ -7606,7 +7617,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" ht="135" spans="1:8">
+    <row r="29" ht="135" hidden="1" spans="1:8">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -7629,7 +7640,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" ht="405" spans="1:8">
+    <row r="30" ht="405" hidden="1" spans="1:8">
       <c r="A30" t="s">
         <v>149</v>
       </c>
@@ -7652,7 +7663,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" ht="337.5" spans="1:8">
+    <row r="31" ht="337.5" hidden="1" spans="1:8">
       <c r="A31" t="s">
         <v>149</v>
       </c>
@@ -7678,7 +7689,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" ht="409.5" spans="1:8">
+    <row r="32" ht="409.5" hidden="1" spans="1:8">
       <c r="A32" t="s">
         <v>149</v>
       </c>
@@ -7704,7 +7715,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" ht="270" spans="1:8">
+    <row r="33" ht="270" hidden="1" spans="1:8">
       <c r="A33" t="s">
         <v>149</v>
       </c>
@@ -7730,7 +7741,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="34" ht="351" spans="1:8">
+    <row r="34" ht="351" hidden="1" spans="1:8">
       <c r="A34" t="s">
         <v>149</v>
       </c>
@@ -7756,7 +7767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" ht="337.5" spans="1:8">
+    <row r="35" ht="337.5" hidden="1" spans="1:8">
       <c r="A35" t="s">
         <v>175</v>
       </c>
@@ -7782,7 +7793,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" ht="378" spans="1:8">
+    <row r="36" ht="378" hidden="1" spans="1:8">
       <c r="A36" t="s">
         <v>181</v>
       </c>
@@ -7805,7 +7816,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" ht="162" spans="1:8">
+    <row r="37" ht="162" hidden="1" spans="1:8">
       <c r="A37" t="s">
         <v>187</v>
       </c>
@@ -7828,7 +7839,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" ht="256.5" spans="1:8">
+    <row r="38" ht="256.5" hidden="1" spans="1:8">
       <c r="A38" t="s">
         <v>187</v>
       </c>
@@ -7851,7 +7862,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" ht="283.5" spans="1:8">
+    <row r="39" ht="283.5" hidden="1" spans="1:8">
       <c r="A39" t="s">
         <v>187</v>
       </c>
@@ -7874,7 +7885,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" ht="148.5" spans="1:8">
+    <row r="40" ht="148.5" hidden="1" spans="1:8">
       <c r="A40" t="s">
         <v>187</v>
       </c>
@@ -7897,7 +7908,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" ht="409.5" spans="1:8">
+    <row r="41" ht="409.5" hidden="1" spans="1:8">
       <c r="A41" t="s">
         <v>187</v>
       </c>
@@ -7923,7 +7934,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" ht="202.5" spans="1:8">
+    <row r="42" ht="202.5" hidden="1" spans="1:8">
       <c r="A42" t="s">
         <v>187</v>
       </c>
@@ -7946,7 +7957,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="43" ht="409.5" spans="1:8">
+    <row r="43" ht="409.5" hidden="1" spans="1:8">
       <c r="A43" t="s">
         <v>187</v>
       </c>
@@ -7969,7 +7980,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="44" ht="409.5" spans="1:8">
+    <row r="44" ht="409.5" hidden="1" spans="1:8">
       <c r="A44" t="s">
         <v>187</v>
       </c>
@@ -7992,7 +8003,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="45" ht="409.5" spans="1:8">
+    <row r="45" ht="409.5" hidden="1" spans="1:8">
       <c r="A45" t="s">
         <v>187</v>
       </c>
@@ -8018,7 +8029,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="46" ht="409.5" spans="1:8">
+    <row r="46" ht="409.5" hidden="1" spans="1:8">
       <c r="A46" t="s">
         <v>187</v>
       </c>
@@ -8044,7 +8055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" ht="409.5" spans="1:8">
+    <row r="47" ht="409.5" hidden="1" spans="1:8">
       <c r="A47" t="s">
         <v>187</v>
       </c>
@@ -8070,7 +8081,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="48" ht="409.5" spans="1:8">
+    <row r="48" ht="409.5" hidden="1" spans="1:8">
       <c r="A48" t="s">
         <v>243</v>
       </c>
@@ -8093,7 +8104,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="49" ht="409.5" spans="1:8">
+    <row r="49" ht="409.5" hidden="1" spans="1:8">
       <c r="A49" t="s">
         <v>249</v>
       </c>
@@ -8116,7 +8127,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="50" ht="409.5" spans="1:8">
+    <row r="50" ht="409.5" hidden="1" spans="1:8">
       <c r="A50" t="s">
         <v>249</v>
       </c>
@@ -8139,7 +8150,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" ht="409.5" spans="1:8">
+    <row r="51" ht="409.5" hidden="1" spans="1:8">
       <c r="A51" t="s">
         <v>249</v>
       </c>
@@ -8165,7 +8176,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="52" ht="364.5" spans="1:8">
+    <row r="52" ht="364.5" hidden="1" spans="1:8">
       <c r="A52" t="s">
         <v>265</v>
       </c>
@@ -8191,7 +8202,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" ht="409.5" spans="1:8">
+    <row r="53" ht="409.5" hidden="1" spans="1:8">
       <c r="A53" t="s">
         <v>271</v>
       </c>
@@ -8217,7 +8228,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" ht="409.5" spans="1:8">
+    <row r="54" ht="409.5" hidden="1" spans="1:8">
       <c r="A54" t="s">
         <v>271</v>
       </c>
@@ -8243,7 +8254,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" ht="409.5" spans="1:8">
+    <row r="55" ht="409.5" hidden="1" spans="1:8">
       <c r="A55" t="s">
         <v>271</v>
       </c>
@@ -8266,7 +8277,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="56" ht="405" spans="1:8">
+    <row r="56" ht="405" hidden="1" spans="1:8">
       <c r="A56" t="s">
         <v>287</v>
       </c>
@@ -8292,7 +8303,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" ht="351" spans="1:8">
+    <row r="57" ht="351" hidden="1" spans="1:8">
       <c r="A57" t="s">
         <v>287</v>
       </c>
@@ -8318,7 +8329,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" ht="409.5" spans="1:8">
+    <row r="58" ht="409.5" hidden="1" spans="1:8">
       <c r="A58" t="s">
         <v>287</v>
       </c>
@@ -8341,7 +8352,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" ht="409.5" spans="1:8">
+    <row r="59" ht="409.5" hidden="1" spans="1:8">
       <c r="A59" t="s">
         <v>287</v>
       </c>
@@ -8367,7 +8378,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="60" ht="351" spans="1:8">
+    <row r="60" ht="351" hidden="1" spans="1:8">
       <c r="A60" t="s">
         <v>287</v>
       </c>
@@ -8390,7 +8401,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="61" ht="409.5" spans="1:8">
+    <row r="61" ht="409.5" hidden="1" spans="1:8">
       <c r="A61" t="s">
         <v>313</v>
       </c>
@@ -8416,7 +8427,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" ht="351" spans="1:8">
+    <row r="62" ht="351" hidden="1" spans="1:8">
       <c r="A62" t="s">
         <v>313</v>
       </c>
@@ -8439,7 +8450,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="63" ht="409.5" spans="1:8">
+    <row r="63" ht="409.5" hidden="1" spans="1:8">
       <c r="A63" t="s">
         <v>324</v>
       </c>
@@ -8465,7 +8476,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" ht="324" spans="1:8">
+    <row r="64" ht="324" hidden="1" spans="1:8">
       <c r="A64" t="s">
         <v>324</v>
       </c>
@@ -8491,7 +8502,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="65" ht="409.5" spans="1:8">
+    <row r="65" ht="409.5" hidden="1" spans="1:8">
       <c r="A65" t="s">
         <v>335</v>
       </c>
@@ -8517,7 +8528,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" ht="409.5" spans="1:8">
+    <row r="66" ht="409.5" hidden="1" spans="1:8">
       <c r="A66" t="s">
         <v>335</v>
       </c>
@@ -8540,7 +8551,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="67" ht="148.5" spans="1:8">
+    <row r="67" ht="148.5" hidden="1" spans="1:8">
       <c r="A67" t="s">
         <v>346</v>
       </c>
@@ -8566,7 +8577,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" ht="229.5" spans="1:8">
+    <row r="68" ht="229.5" hidden="1" spans="1:8">
       <c r="A68" t="s">
         <v>352</v>
       </c>
@@ -8589,7 +8600,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="69" ht="364.5" spans="1:8">
+    <row r="69" ht="364.5" hidden="1" spans="1:8">
       <c r="A69" t="s">
         <v>358</v>
       </c>
@@ -8615,7 +8626,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="70" ht="189" spans="1:8">
+    <row r="70" ht="189" hidden="1" spans="1:8">
       <c r="A70" t="s">
         <v>358</v>
       </c>
@@ -8641,7 +8652,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" ht="243" spans="1:8">
+    <row r="71" ht="243" hidden="1" spans="1:8">
       <c r="A71" t="s">
         <v>358</v>
       </c>
@@ -8667,7 +8678,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="72" ht="121.5" spans="1:8">
+    <row r="72" ht="121.5" hidden="1" spans="1:8">
       <c r="A72" t="s">
         <v>358</v>
       </c>
@@ -8690,7 +8701,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="73" ht="270" spans="1:8">
+    <row r="73" ht="270" hidden="1" spans="1:8">
       <c r="A73" t="s">
         <v>358</v>
       </c>
@@ -8713,7 +8724,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="74" ht="297" spans="1:8">
+    <row r="74" ht="297" hidden="1" spans="1:8">
       <c r="A74" t="s">
         <v>358</v>
       </c>
@@ -8739,7 +8750,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75" ht="364.5" spans="1:8">
+    <row r="75" ht="364.5" hidden="1" spans="1:8">
       <c r="A75" t="s">
         <v>358</v>
       </c>
@@ -8762,7 +8773,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="76" ht="409.5" spans="1:8">
+    <row r="76" ht="409.5" hidden="1" spans="1:8">
       <c r="A76" t="s">
         <v>358</v>
       </c>
@@ -8788,7 +8799,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" ht="297" spans="1:8">
+    <row r="77" ht="297" hidden="1" spans="1:8">
       <c r="A77" t="s">
         <v>381</v>
       </c>
@@ -8814,7 +8825,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" ht="409.5" spans="1:8">
+    <row r="78" ht="409.5" hidden="1" spans="1:8">
       <c r="A78" t="s">
         <v>387</v>
       </c>
@@ -8840,7 +8851,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="79" ht="409.5" spans="1:8">
+    <row r="79" ht="409.5" hidden="1" spans="1:8">
       <c r="A79" t="s">
         <v>393</v>
       </c>
@@ -8866,7 +8877,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" ht="310.5" spans="1:8">
+    <row r="80" ht="310.5" hidden="1" spans="1:8">
       <c r="A80" t="s">
         <v>393</v>
       </c>
@@ -8926,13 +8937,13 @@
         <v>410</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>409</v>
@@ -8949,19 +8960,19 @@
         <v>404</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>14</v>
@@ -8975,19 +8986,19 @@
         <v>404</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>38</v>
@@ -8998,19 +9009,19 @@
         <v>404</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>14</v>
@@ -9024,19 +9035,19 @@
         <v>404</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>21</v>
@@ -9050,19 +9061,19 @@
         <v>404</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>38</v>
@@ -9073,19 +9084,19 @@
         <v>404</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>21</v>
@@ -9094,47 +9105,47 @@
         <v>76</v>
       </c>
     </row>
-    <row r="89" ht="391.5" spans="1:8">
+    <row r="89" ht="391.5" hidden="1" spans="1:8">
       <c r="A89" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="90" ht="409.5" spans="1:8">
+    <row r="90" ht="409.5" hidden="1" spans="1:8">
       <c r="A90" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>21</v>
@@ -9145,6 +9156,11 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H90" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <customFilters>
+        <customFilter operator="equal" val="altanalyze"/>
+      </customFilters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
